--- a/models/9022_DCF_Model_20260906.xlsx
+++ b/models/9022_DCF_Model_20260906.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ryosuke0923\ryosuke-japanese-equity-research\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BB4C489-0402-4F25-AA37-74B11EE02166}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DF29802-3F77-4B50-AB70-7C9180E9F4D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="360">
   <si>
     <t>DISCLAIMER: This is a sample analysis for demonstration purposes only. It does not constitute investment advice.</t>
   </si>
@@ -780,7 +780,7 @@
     <t>-</t>
   </si>
   <si>
-    <t>Generated by pipeline on 2026-09-06 19:31, template rev 63983ab</t>
+    <t>Generated by pipeline on 2026-09-06 23:21, template rev 041abe3</t>
   </si>
   <si>
     <t>初期生成（手修正なし）</t>
@@ -828,6 +828,12 @@
     <t>value</t>
   </si>
   <si>
+    <t>annual_doc_ids</t>
+  </si>
+  <si>
+    <t>2026-03-31=S100YD7H, 2025-03-31=S100W2Z6, 2024-03-31=S100TNI7, 2023-03-31=S100R0WN, 2022-03-31=S100OC2F</t>
+  </si>
+  <si>
     <t>auto_log_entries</t>
   </si>
   <si>
@@ -999,6 +1005,12 @@
     <t>0.114247</t>
   </si>
   <si>
+    <t>disclosure_basis_date</t>
+  </si>
+  <si>
+    <t>2026-03-31</t>
+  </si>
+  <si>
     <t>fs_year_coverage</t>
   </si>
   <si>
@@ -1026,7 +1038,7 @@
     <t>generated_at</t>
   </si>
   <si>
-    <t>2026-09-06 19:31:00</t>
+    <t>2026-09-06 23:21:12</t>
   </si>
   <si>
     <t>guidance_note</t>
@@ -1098,7 +1110,7 @@
     <t>template_rev</t>
   </si>
   <si>
-    <t>63983ab</t>
+    <t>041abe3</t>
   </si>
   <si>
     <t>ticker</t>
@@ -6485,7 +6497,7 @@
   <sheetPr>
     <tabColor rgb="FF808080"/>
   </sheetPr>
-  <dimension ref="B2:G64"/>
+  <dimension ref="B2:G66"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -6623,15 +6635,15 @@
         <v>270</v>
       </c>
       <c r="C17" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="14" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C18" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="14" x14ac:dyDescent="0.3">
@@ -6671,23 +6683,23 @@
         <v>281</v>
       </c>
       <c r="C23" t="s">
-        <v>4</v>
+        <v>282</v>
       </c>
     </row>
     <row r="24" spans="2:3" ht="14" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C24" t="s">
-        <v>246</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="2:3" ht="14" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C25" t="s">
-        <v>284</v>
+        <v>246</v>
       </c>
     </row>
     <row r="26" spans="2:3" ht="14" x14ac:dyDescent="0.3">
@@ -6695,23 +6707,23 @@
         <v>285</v>
       </c>
       <c r="C26" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
     </row>
     <row r="27" spans="2:3" ht="14" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C27" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="28" spans="2:3" ht="14" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C28" t="s">
-        <v>288</v>
+        <v>274</v>
       </c>
     </row>
     <row r="29" spans="2:3" ht="14" x14ac:dyDescent="0.3">
@@ -6735,31 +6747,31 @@
         <v>293</v>
       </c>
       <c r="C31" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="2:3" ht="14" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C32" t="s">
-        <v>272</v>
+        <v>290</v>
       </c>
     </row>
     <row r="33" spans="2:3" ht="14" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C33" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
     </row>
     <row r="34" spans="2:3" ht="14" x14ac:dyDescent="0.3">
       <c r="B34" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C34" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
     </row>
     <row r="35" spans="2:3" ht="14" x14ac:dyDescent="0.3">
@@ -6839,15 +6851,15 @@
         <v>316</v>
       </c>
       <c r="C44" t="s">
-        <v>276</v>
+        <v>317</v>
       </c>
     </row>
     <row r="45" spans="2:3" ht="14" x14ac:dyDescent="0.3">
       <c r="B45" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C45" t="s">
-        <v>318</v>
+        <v>278</v>
       </c>
     </row>
     <row r="46" spans="2:3" ht="14" x14ac:dyDescent="0.3">
@@ -6999,6 +7011,22 @@
         <v>355</v>
       </c>
       <c r="C64" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B65" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="C65" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="66" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B66" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="C66" t="s">
         <v>209</v>
       </c>
     </row>
